--- a/assessment_forms/012_project_management_maturity_assessment_application_form--assessment_forms.xlsx
+++ b/assessment_forms/012_project_management_maturity_assessment_application_form--assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>project_management_process_innovation_sustainability_roadmap</t>
+          <t>project_management_process_innovation_sustainability_roadmap_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Project Management Process Innovation Sustainability Roadmap</t>
+          <t>Project Management Process Innovation Sustainability Roadmap 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>project_management_process_innovation_sustainability_roadmap_implemented</t>
+          <t>project_management_process_innovation_sustainability_roadmap_implemented_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Project Management Process Innovation Sustainability Roadmap Implemented</t>
+          <t>Project Management Process Innovation Sustainability Roadmap Implemented 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>project_management_process_innovation_sustainability_success</t>
+          <t>project_management_process_innovation_sustainability_success_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Project Management Process Innovation Sustainability Success</t>
+          <t>Project Management Process Innovation Sustainability Success 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>project_management_process_innovation_sustainability_success_implemented</t>
+          <t>project_management_process_innovation_sustainability_success_implemented_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1177,12 +1177,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'project_manager'}</t>
+          <t>project_manager</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Project Manager'}</t>
+          <t>Project Manager</t>
         </is>
       </c>
     </row>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'project_manager_and_team_members'}</t>
+          <t>project_manager_and_team_members</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Project Manager and team members'}</t>
+          <t>Project Manager and team members</t>
         </is>
       </c>
     </row>
@@ -1211,12 +1211,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'project_manager_and_all_team_members'}</t>
+          <t>project_manager_and_all_team_members</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Project Manager and all team members'}</t>
+          <t>Project Manager and all team members</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'beginner'}</t>
+          <t>beginner</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Beginner'}</t>
+          <t>Beginner</t>
         </is>
       </c>
     </row>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'intermediate'}</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Intermediate'}</t>
+          <t>Intermediate</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1262,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'advanced'}</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Advanced'}</t>
+          <t>Advanced</t>
         </is>
       </c>
     </row>
@@ -1279,12 +1279,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'expert'}</t>
+          <t>expert</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Expert'}</t>
+          <t>Expert</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'project_with_well-defined_scope_and_purpose'}</t>
+          <t>project_with_well-defined_scope_and_purpose</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Project with well-defined scope and purpose'}</t>
+          <t>Project with well-defined scope and purpose</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'project_with_partially_defined_scope_and_purpose'}</t>
+          <t>project_with_partially_defined_scope_and_purpose</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Project with partially defined scope and purpose'}</t>
+          <t>Project with partially defined scope and purpose</t>
         </is>
       </c>
     </row>
@@ -1330,12 +1330,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'project_with_undefined_scope_and_purpose'}</t>
+          <t>project_with_undefined_scope_and_purpose</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Project with undefined scope and purpose'}</t>
+          <t>Project with undefined scope and purpose</t>
         </is>
       </c>
     </row>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'multiple_phases_with_well-defined_activities'}</t>
+          <t>multiple_phases_with_well-defined_activities</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Multiple phases with well-defined activities'}</t>
+          <t>Multiple phases with well-defined activities</t>
         </is>
       </c>
     </row>
@@ -1364,12 +1364,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'multiple_phases_with_partially_defined_activities'}</t>
+          <t>multiple_phases_with_partially_defined_activities</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Multiple phases with partially defined activities'}</t>
+          <t>Multiple phases with partially defined activities</t>
         </is>
       </c>
     </row>
@@ -1381,12 +1381,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'single_phase_with_well-defined_activities'}</t>
+          <t>single_phase_with_well-defined_activities</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Single phase with well-defined activities'}</t>
+          <t>Single phase with well-defined activities</t>
         </is>
       </c>
     </row>
@@ -1398,12 +1398,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'strongly_agree'}</t>
+          <t>strongly_agree</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Strongly agree'}</t>
+          <t>Strongly agree</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1432,12 +1432,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'strongly_disagree'}</t>
+          <t>strongly_disagree</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Strongly disagree'}</t>
+          <t>Strongly disagree</t>
         </is>
       </c>
     </row>
@@ -1449,12 +1449,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'strongly_agree'}</t>
+          <t>strongly_agree</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Strongly agree'}</t>
+          <t>Strongly agree</t>
         </is>
       </c>
     </row>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1483,12 +1483,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'strongly_disagree'}</t>
+          <t>strongly_disagree</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Strongly disagree'}</t>
+          <t>Strongly disagree</t>
         </is>
       </c>
     </row>
@@ -1500,12 +1500,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1517,12 +1517,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1534,12 +1534,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1568,12 +1568,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'strongly_agree'}</t>
+          <t>strongly_agree</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'Strongly agree'}</t>
+          <t>Strongly agree</t>
         </is>
       </c>
     </row>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1602,12 +1602,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'strongly_disagree'}</t>
+          <t>strongly_disagree</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'Strongly disagree'}</t>
+          <t>Strongly disagree</t>
         </is>
       </c>
     </row>
@@ -1619,12 +1619,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_'strongly_agree'}</t>
+          <t>strongly_agree</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 'Strongly agree'}</t>
+          <t>Strongly agree</t>
         </is>
       </c>
     </row>
@@ -1636,12 +1636,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1653,12 +1653,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_'strongly_disagree'}</t>
+          <t>strongly_disagree</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 'Strongly disagree'}</t>
+          <t>Strongly disagree</t>
         </is>
       </c>
     </row>
@@ -1670,12 +1670,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_'strongly_agree'}</t>
+          <t>strongly_agree</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': 'Strongly agree'}</t>
+          <t>Strongly agree</t>
         </is>
       </c>
     </row>
@@ -1687,12 +1687,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'value':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'value': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'value':_'strongly_disagree'}</t>
+          <t>strongly_disagree</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'value': 'Strongly disagree'}</t>
+          <t>Strongly disagree</t>
         </is>
       </c>
     </row>
@@ -1721,12 +1721,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1738,12 +1738,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1772,12 +1772,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'value':_'strongly_agree'}</t>
+          <t>strongly_agree</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'value': 'Strongly agree'}</t>
+          <t>Strongly agree</t>
         </is>
       </c>
     </row>
@@ -1840,12 +1840,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'value':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'value': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1857,12 +1857,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'value':_'strongly_disagree'}</t>
+          <t>strongly_disagree</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'value': 'Strongly disagree'}</t>
+          <t>Strongly disagree</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'value':_'strongly_agree'}</t>
+          <t>strongly_agree</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'value': 'Strongly agree'}</t>
+          <t>Strongly agree</t>
         </is>
       </c>
     </row>
@@ -1891,12 +1891,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'value':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'value': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1908,12 +1908,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'value':_'strongly_disagree'}</t>
+          <t>strongly_disagree</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'value': 'Strongly disagree'}</t>
+          <t>Strongly disagree</t>
         </is>
       </c>
     </row>
@@ -1925,12 +1925,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1942,131 +1942,131 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>project_management_process_innovation_sustainability_roadmap_choices</t>
+          <t>project_management_process_innovation_sustainability_roadmap_2_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>project_management_process_innovation_sustainability_roadmap_choices</t>
+          <t>project_management_process_innovation_sustainability_roadmap_2_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>project_management_process_innovation_sustainability_roadmap_implemented_choices</t>
+          <t>project_management_process_innovation_sustainability_roadmap_implemented_2_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>project_management_process_innovation_sustainability_roadmap_implemented_choices</t>
+          <t>project_management_process_innovation_sustainability_roadmap_implemented_2_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>project_management_process_innovation_sustainability_success_choices</t>
+          <t>project_management_process_innovation_sustainability_success_2_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'value':_'strongly_agree'}</t>
+          <t>strongly_agree</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'value': 'Strongly agree'}</t>
+          <t>Strongly agree</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>project_management_process_innovation_sustainability_success_choices</t>
+          <t>project_management_process_innovation_sustainability_success_2_choices</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'value':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'value': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>project_management_process_innovation_sustainability_success_choices</t>
+          <t>project_management_process_innovation_sustainability_success_2_choices</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'value':_'strongly_disagree'}</t>
+          <t>strongly_disagree</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'value': 'Strongly disagree'}</t>
+          <t>Strongly disagree</t>
         </is>
       </c>
     </row>
@@ -2078,12 +2078,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'value':_'strongly_agree'}</t>
+          <t>strongly_agree</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'value': 'Strongly agree'}</t>
+          <t>Strongly agree</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'value':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'value': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -2112,12 +2112,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'value':_'strongly_disagree'}</t>
+          <t>strongly_disagree</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'value': 'Strongly disagree'}</t>
+          <t>Strongly disagree</t>
         </is>
       </c>
     </row>
@@ -2129,12 +2129,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2146,46 +2146,46 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>project_management_process_innovation_sustainability_success_implemented_choices</t>
+          <t>project_management_process_innovation_sustainability_success_implemented_2_choices</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>project_management_process_innovation_sustainability_success_implemented_choices</t>
+          <t>project_management_process_innovation_sustainability_success_implemented_2_choices</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2197,12 +2197,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2231,12 +2231,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>{'value':_'strongly_agree'}</t>
+          <t>strongly_agree</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>{'value': 'Strongly agree'}</t>
+          <t>Strongly agree</t>
         </is>
       </c>
     </row>
@@ -2248,12 +2248,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>{'value':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>{'value': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -2265,12 +2265,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>{'value':_'strongly_disagree'}</t>
+          <t>strongly_disagree</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>{'value': 'Strongly disagree'}</t>
+          <t>Strongly disagree</t>
         </is>
       </c>
     </row>
